--- a/study_case_model/scenario_variables/price_scenarios151.xlsx
+++ b/study_case_model/scenario_variables/price_scenarios151.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29416.702360045</v>
+        <v>29.416702360045</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24681.80530718405</v>
+        <v>24.68180530718405</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28855.29538016771</v>
+        <v>28.8552953801677</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28370.56492355233</v>
+        <v>28.37056492355233</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25118.72554310184</v>
+        <v>25.11872554310184</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27508.87169431866</v>
+        <v>27.50887169431866</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32907.87300943365</v>
+        <v>32.90787300943364</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27875.74516374544</v>
+        <v>27.87574516374544</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>26915.7348140006</v>
+        <v>26.9157348140006</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29492.86164780707</v>
+        <v>29.49286164780708</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>25337.55779404849</v>
+        <v>25.33755779404849</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28531.74778531074</v>
+        <v>28.53174778531074</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22263.8553050907</v>
+        <v>22.2638553050907</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25704.24341457162</v>
+        <v>25.70424341457162</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26985.25377237739</v>
+        <v>26.98525377237738</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31563.90729040323</v>
+        <v>31.56390729040323</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28459.32282626804</v>
+        <v>28.45932282626804</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27953.92442875578</v>
+        <v>27.95392442875578</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29201.91302243842</v>
+        <v>29.20191302243843</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20103.23222737026</v>
+        <v>20.10323222737026</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27009.71221377941</v>
+        <v>27.00971221377941</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27121.02426026036</v>
+        <v>27.12102426026036</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30948.8505124</v>
+        <v>30.94885051240001</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31516.37717075344</v>
+        <v>31.51637717075344</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>18623.13958381968</v>
+        <v>18.62313958381968</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/price_scenarios151.xlsx
+++ b/study_case_model/scenario_variables/price_scenarios151.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.416702360045</v>
+        <v>27.12445164247194</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.68180530718405</v>
+        <v>33.12476542513664</v>
       </c>
     </row>
     <row r="4">
@@ -491,11 +491,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.8552953801677</v>
+        <v>25.66029609589989</v>
       </c>
     </row>
     <row r="5">
@@ -507,11 +507,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.37056492355233</v>
+        <v>24.73889828712912</v>
       </c>
     </row>
     <row r="6">
@@ -523,11 +523,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25.11872554310184</v>
+        <v>32.73144265246271</v>
       </c>
     </row>
     <row r="7">
@@ -535,15 +535,15 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27.50887169431866</v>
+        <v>21.52675764849945</v>
       </c>
     </row>
     <row r="8">
@@ -555,11 +555,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32.90787300943364</v>
+        <v>29.58438532176227</v>
       </c>
     </row>
     <row r="9">
@@ -571,11 +571,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27.87574516374544</v>
+        <v>22.73884824827317</v>
       </c>
     </row>
     <row r="10">
@@ -587,11 +587,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>26.9157348140006</v>
+        <v>20.89536729880186</v>
       </c>
     </row>
     <row r="11">
@@ -603,11 +603,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29.49286164780708</v>
+        <v>28.36702195512321</v>
       </c>
     </row>
     <row r="12">
@@ -615,15 +615,15 @@
         <v>3</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>25.33755779404849</v>
+        <v>32.33182477894351</v>
       </c>
     </row>
     <row r="13">
@@ -631,15 +631,15 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.53174778531074</v>
+        <v>27.07850506055134</v>
       </c>
     </row>
     <row r="14">
@@ -651,11 +651,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22.2638553050907</v>
+        <v>28.65435058310896</v>
       </c>
     </row>
     <row r="15">
@@ -667,11 +667,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.70424341457162</v>
+        <v>27.58181851634063</v>
       </c>
     </row>
     <row r="16">
@@ -683,11 +683,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26.98525377237738</v>
+        <v>19.70369118958031</v>
       </c>
     </row>
     <row r="17">
@@ -695,15 +695,15 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31.56390729040323</v>
+        <v>26.19800294850597</v>
       </c>
     </row>
     <row r="18">
@@ -711,15 +711,15 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28.45932282626804</v>
+        <v>28.64299488995622</v>
       </c>
     </row>
     <row r="19">
@@ -727,15 +727,15 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27.95392442875578</v>
+        <v>30.03270736580942</v>
       </c>
     </row>
     <row r="20">
@@ -747,11 +747,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.20191302243843</v>
+        <v>30.02401805469523</v>
       </c>
     </row>
     <row r="21">
@@ -763,11 +763,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20.10323222737026</v>
+        <v>22.60508485551988</v>
       </c>
     </row>
     <row r="22">
@@ -775,15 +775,15 @@
         <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27.00971221377941</v>
+        <v>27.20403629644433</v>
       </c>
     </row>
     <row r="23">
@@ -791,15 +791,15 @@
         <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.12102426026036</v>
+        <v>27.01791063860232</v>
       </c>
     </row>
     <row r="24">
@@ -807,15 +807,15 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30.94885051240001</v>
+        <v>28.38258964271438</v>
       </c>
     </row>
     <row r="25">
@@ -823,15 +823,15 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.51637717075344</v>
+        <v>28.23842373918275</v>
       </c>
     </row>
     <row r="26">
@@ -843,11 +843,91 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>31.73126233136204</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>30.45400862326081</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>22.93509557161339</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>27.22340934879423</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>30.82959752759295</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>EASINGTON</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>18.62313958381968</v>
+      <c r="D31" t="n">
+        <v>29.95760343457476</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/price_scenarios151.xlsx
+++ b/study_case_model/scenario_variables/price_scenarios151.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="10">
   <si>
     <t>stage</t>
   </si>
@@ -26,6 +26,24 @@
   </si>
   <si>
     <t>price</t>
+  </si>
+  <si>
+    <t>ZEEBRUGGE</t>
+  </si>
+  <si>
+    <t>EMDEN</t>
+  </si>
+  <si>
+    <t>ST.FERGUS</t>
+  </si>
+  <si>
+    <t>DORNUM</t>
+  </si>
+  <si>
+    <t>DUNKERQUE</t>
+  </si>
+  <si>
+    <t>EASINGTON</t>
   </si>
 </sst>
 </file>
@@ -383,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -400,6 +418,426 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>27.12445164247194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>33.12476542513664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>25.66029609589989</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>24.73889828712912</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>32.73144265246271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>21.52675764849945</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>29.58438532176227</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>22.73884824827317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>20.89536729880186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>28.36702195512321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>32.33182477894351</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>27.07850506055134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>28.65435058310896</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>27.58181851634063</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>3</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>19.70369118958031</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>26.19800294850597</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>28.64299488995622</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>30.03270736580942</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>30.02401805469523</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>22.60508485551988</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>27.20403629644433</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>27.01791063860232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24">
+        <v>28.38258964271438</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25">
+        <v>28.23842373918275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26">
+        <v>31.73126233136204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>30.45400862326081</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>3</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28">
+        <v>22.93509557161339</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29">
+        <v>27.22340934879423</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>30.82959752759295</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31">
+        <v>29.95760343457476</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/study_case_model/scenario_variables/price_scenarios151.xlsx
+++ b/study_case_model/scenario_variables/price_scenarios151.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.12445164247194</v>
+        <v>26.7905402530697</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.12476542513664</v>
+        <v>27.2259749722089</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.66029609589989</v>
+        <v>23.43964183942517</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.73889828712912</v>
+        <v>25.55701280286056</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.73144265246271</v>
+        <v>28.12297957397958</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.52675764849945</v>
+        <v>25.93099674516278</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29.58438532176227</v>
+        <v>26.05130545578145</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22.73884824827317</v>
+        <v>29.09188819223419</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.89536729880186</v>
+        <v>33.18295538632918</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28.36702195512321</v>
+        <v>29.65768934105139</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32.33182477894351</v>
+        <v>28.99957017237241</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.07850506055134</v>
+        <v>22.42454927764545</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28.65435058310896</v>
+        <v>26.87618408057382</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>27.58181851634063</v>
+        <v>33.02572071220121</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19.70369118958031</v>
+        <v>26.28084076132626</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26.19800294850597</v>
+        <v>25.68626358356217</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28.64299488995622</v>
+        <v>30.47913147758954</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>30.03270736580942</v>
+        <v>34.47408780118976</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30.02401805469523</v>
+        <v>29.41599022578121</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>22.60508485551988</v>
+        <v>29.95470067643151</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27.20403629644433</v>
+        <v>27.11025621467063</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.01791063860232</v>
+        <v>26.95946824648871</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.38258964271438</v>
+        <v>26.62201932970249</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.23842373918275</v>
+        <v>24.73859011707207</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31.73126233136204</v>
+        <v>28.45051235567749</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>30.45400862326081</v>
+        <v>29.67782212662053</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>22.93509557161339</v>
+        <v>29.07571881282962</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>27.22340934879423</v>
+        <v>30.72264709978333</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>30.82959752759295</v>
+        <v>30.89435207538845</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>29.95760343457476</v>
+        <v>29.78470671206263</v>
       </c>
     </row>
   </sheetData>
